--- a/data/trans_orig/P37-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2007</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2007 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>88198</t>
+          <t>89337</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125997</t>
+          <t>127375</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>83367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>122942</t>
+          <t>120756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>183856</t>
+          <t>180526</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235352</t>
+          <t>235485</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>17,05%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>568015</t>
+          <t>566637</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>605814</t>
+          <t>604675</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>564493</t>
+          <t>566679</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>601883</t>
+          <t>604068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1146095</t>
+          <t>1145962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1197591</t>
+          <t>1200921</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,96%</t>
+          <t>82,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,69%</t>
+          <t>86,93%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>112966</t>
+          <t>114111</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>156830</t>
+          <t>157296</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136353</t>
+          <t>134080</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183840</t>
+          <t>183121</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,08%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>262886</t>
+          <t>260265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>325112</t>
+          <t>327378</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>804970</t>
+          <t>804504</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>848834</t>
+          <t>847689</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>784553</t>
+          <t>785272</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>832040</t>
+          <t>834313</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1605081</t>
+          <t>1602815</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1667307</t>
+          <t>1669928</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>86,52%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>71338</t>
+          <t>70692</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106336</t>
+          <t>106417</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91030</t>
+          <t>91308</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129348</t>
+          <t>130458</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172606</t>
+          <t>172056</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225550</t>
+          <t>225306</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>571259</t>
+          <t>571178</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606257</t>
+          <t>606903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>553512</t>
+          <t>552402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>591830</t>
+          <t>591552</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1134905</t>
+          <t>1135149</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1187849</t>
+          <t>1188399</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107954</t>
+          <t>107717</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>146708</t>
+          <t>148747</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>142348</t>
+          <t>141972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>189625</t>
+          <t>190592</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>263272</t>
+          <t>259818</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>326001</t>
+          <t>320656</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>794664</t>
+          <t>792625</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>833418</t>
+          <t>833655</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>848987</t>
+          <t>848020</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896264</t>
+          <t>896640</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1653983</t>
+          <t>1659328</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1716712</t>
+          <t>1720166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,54%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,88%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>415220</t>
+          <t>417913</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>490166</t>
+          <t>490096</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>491392</t>
+          <t>494083</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>576847</t>
+          <t>574991</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>936157</t>
+          <t>933527</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1051755</t>
+          <t>1045896</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2784613</t>
+          <t>2784683</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2859559</t>
+          <t>2856866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2800453</t>
+          <t>2802309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2885908</t>
+          <t>2883217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5600324</t>
+          <t>5606183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5715922</t>
+          <t>5718552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>85,97%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2012</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2012 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>122007</t>
+          <t>121851</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>163918</t>
+          <t>165520</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>112629</t>
+          <t>111995</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>153098</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>16,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247095</t>
+          <t>245220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>305660</t>
+          <t>303989</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>538524</t>
+          <t>536922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>580435</t>
+          <t>580591</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,63%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>543952</t>
+          <t>542014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>584421</t>
+          <t>585055</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,84%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1093832</t>
+          <t>1095503</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1152397</t>
+          <t>1154272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,34%</t>
+          <t>82,48%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>157076</t>
+          <t>154712</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>207122</t>
+          <t>204455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>168969</t>
+          <t>165846</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221527</t>
+          <t>221269</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>335541</t>
+          <t>336098</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408342</t>
+          <t>408625</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,94%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>810825</t>
+          <t>813492</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>860871</t>
+          <t>863235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>809586</t>
+          <t>809844</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>862144</t>
+          <t>865267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1640718</t>
+          <t>1640435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1713519</t>
+          <t>1712962</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>83,6%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99960</t>
+          <t>98600</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141336</t>
+          <t>142957</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111885</t>
+          <t>112573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>156312</t>
+          <t>157259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>219920</t>
+          <t>221989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282754</t>
+          <t>285226</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>615282</t>
+          <t>613661</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>656658</t>
+          <t>658018</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>620862</t>
+          <t>619915</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>665289</t>
+          <t>664601</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>85,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1251038</t>
+          <t>1248566</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1313872</t>
+          <t>1311803</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,53%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>141437</t>
+          <t>140276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>188254</t>
+          <t>189903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>166468</t>
+          <t>167770</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>216446</t>
+          <t>217708</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,58%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>318725</t>
+          <t>321255</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>390853</t>
+          <t>392387</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,65%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>756494</t>
+          <t>754845</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>803311</t>
+          <t>804472</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>835455</t>
+          <t>834193</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885433</t>
+          <t>884131</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,42%</t>
+          <t>79,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1605796</t>
+          <t>1604262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1677924</t>
+          <t>1675394</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,04%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>559635</t>
+          <t>561934</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>654722</t>
+          <t>651223</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,36%</t>
+          <t>16,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>602855</t>
+          <t>603682</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>697599</t>
+          <t>697331</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1188426</t>
+          <t>1180465</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1318334</t>
+          <t>1318056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2767033</t>
+          <t>2770532</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2862120</t>
+          <t>2859821</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,64%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2859639</t>
+          <t>2859907</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2954383</t>
+          <t>2953556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,39%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,05%</t>
+          <t>83,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5660659</t>
+          <t>5660937</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5790567</t>
+          <t>5798528</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2016</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>98255</t>
+          <t>97776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135525</t>
+          <t>135793</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>101393</t>
+          <t>99607</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>141725</t>
+          <t>139958</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>206442</t>
+          <t>208760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261710</t>
+          <t>262241</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,46%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>539275</t>
+          <t>539007</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>576545</t>
+          <t>577024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,92%</t>
+          <t>79,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,44%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>531114</t>
+          <t>532881</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>571446</t>
+          <t>573232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1085929</t>
+          <t>1085398</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1141197</t>
+          <t>1138879</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,68%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>128096</t>
+          <t>126992</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>171652</t>
+          <t>168942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>163825</t>
+          <t>160217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>219666</t>
+          <t>214477</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301619</t>
+          <t>301833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>374495</t>
+          <t>372419</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>850779</t>
+          <t>853489</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>894335</t>
+          <t>895439</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>823247</t>
+          <t>828436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>879088</t>
+          <t>882696</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1690849</t>
+          <t>1692925</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1763725</t>
+          <t>1763511</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,87%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,39%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>105738</t>
+          <t>106400</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>148756</t>
+          <t>149612</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103492</t>
+          <t>102235</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147819</t>
+          <t>148027</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>220369</t>
+          <t>221502</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>281653</t>
+          <t>282110</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,26%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>610796</t>
+          <t>609940</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653814</t>
+          <t>653152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>637192</t>
+          <t>636984</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>681519</t>
+          <t>682776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,82%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262910</t>
+          <t>1262453</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1324194</t>
+          <t>1323061</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,73%</t>
+          <t>85,66%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>124064</t>
+          <t>122313</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>167524</t>
+          <t>165634</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>158327</t>
+          <t>156075</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>211548</t>
+          <t>210376</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294437</t>
+          <t>296146</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>366452</t>
+          <t>364532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,4%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>770043</t>
+          <t>771933</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>813503</t>
+          <t>815254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>832231</t>
+          <t>833403</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>885452</t>
+          <t>887704</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,73%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1614894</t>
+          <t>1616814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1686909</t>
+          <t>1685200</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,05%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>493254</t>
+          <t>496907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>581097</t>
+          <t>576882</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>564712</t>
+          <t>568059</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>659929</t>
+          <t>664023</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,62%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1079768</t>
+          <t>1085633</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1209766</t>
+          <t>1210414</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,44%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2813253</t>
+          <t>2817468</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2901096</t>
+          <t>2897443</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>83,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2884613</t>
+          <t>2880519</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2979830</t>
+          <t>2976483</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,38%</t>
+          <t>81,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5729126</t>
+          <t>5728478</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5859124</t>
+          <t>5853259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,44%</t>
+          <t>84,35%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si se han vacunado de la gripe en la última campaña en 2023</t>
+          <t>Población según si se han vacunado de la gripe en la última campaña en 2023 (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>180195</t>
+          <t>177703</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>225214</t>
+          <t>224456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>237153</t>
+          <t>236220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>276099</t>
+          <t>273629</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>425743</t>
+          <t>423896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>485802</t>
+          <t>487781</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,21%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410227</t>
+          <t>410985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455246</t>
+          <t>457738</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>399271</t>
+          <t>401741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>438217</t>
+          <t>439150</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,89%</t>
+          <t>65,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>825009</t>
+          <t>823030</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>885068</t>
+          <t>886915</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,94%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,66%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>136796</t>
+          <t>121932</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>333366</t>
+          <t>336549</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>319185</t>
+          <t>319719</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>368415</t>
+          <t>367975</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>410220</t>
+          <t>398484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>692452</t>
+          <t>690172</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>859498</t>
+          <t>856315</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1056068</t>
+          <t>1070932</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>589691</t>
+          <t>590131</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>638921</t>
+          <t>638387</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1458519</t>
+          <t>1460799</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1740751</t>
+          <t>1752487</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,47%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>186690</t>
+          <t>184096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>237049</t>
+          <t>235680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,49%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>281411</t>
+          <t>281024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>655423</t>
+          <t>684962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>497413</t>
+          <t>484135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>990182</t>
+          <t>959421</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>30,37%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>58,57%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>467631</t>
+          <t>469000</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>517990</t>
+          <t>520584</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277943</t>
+          <t>248404</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>651955</t>
+          <t>652342</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647864</t>
+          <t>678625</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1140633</t>
+          <t>1153911</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,55%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>69,63%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>302969</t>
+          <t>306608</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>362349</t>
+          <t>367671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>314339</t>
+          <t>324400</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>431440</t>
+          <t>436301</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>638870</t>
+          <t>642055</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>775355</t>
+          <t>776731</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>564482</t>
+          <t>559160</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>623862</t>
+          <t>620223</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>661153</t>
+          <t>656292</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>778254</t>
+          <t>768193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1244069</t>
+          <t>1242693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1380554</t>
+          <t>1377369</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,21%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>772581</t>
+          <t>761251</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1102113</t>
+          <t>1094074</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1277459</t>
+          <t>1272239</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1863471</t>
+          <t>1826627</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>49,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2191821</t>
+          <t>2207379</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2871650</t>
+          <t>2865676</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2357704</t>
+          <t>2365743</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2687236</t>
+          <t>2698566</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1795964</t>
+          <t>1832808</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2381976</t>
+          <t>2387196</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4247602</t>
+          <t>4253576</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4927431</t>
+          <t>4911873</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,66%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P37-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P37-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>89337</t>
+          <t>86885</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>127375</t>
+          <t>127366</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,7 +748,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>83367</t>
+          <t>84612</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>120756</t>
+          <t>121108</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>180526</t>
+          <t>182109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235485</t>
+          <t>233110</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,87%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>566637</t>
+          <t>566646</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>604675</t>
+          <t>607127</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -866,7 +866,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>566679</t>
+          <t>566327</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>604068</t>
+          <t>602823</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1145962</t>
+          <t>1148337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1200921</t>
+          <t>1199338</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,95%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>114111</t>
+          <t>114606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>157296</t>
+          <t>158333</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>134080</t>
+          <t>133612</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>183121</t>
+          <t>182024</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>260265</t>
+          <t>261552</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327378</t>
+          <t>324729</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>804504</t>
+          <t>803467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>847689</t>
+          <t>847194</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,65%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>785272</t>
+          <t>786369</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>834313</t>
+          <t>834781</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1602815</t>
+          <t>1605464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1669928</t>
+          <t>1668641</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,45%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70692</t>
+          <t>71567</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106417</t>
+          <t>109408</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,71%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91308</t>
+          <t>91218</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130458</t>
+          <t>130307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>172056</t>
+          <t>171418</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>225306</t>
+          <t>223991</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>571178</t>
+          <t>568187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>606903</t>
+          <t>606028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>552402</t>
+          <t>552553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>591552</t>
+          <t>591642</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1135149</t>
+          <t>1136464</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1188399</t>
+          <t>1189037</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,4%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107717</t>
+          <t>106536</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>148747</t>
+          <t>149206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>141972</t>
+          <t>143026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>190592</t>
+          <t>191761</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>259818</t>
+          <t>259174</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>320656</t>
+          <t>324325</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>792625</t>
+          <t>792166</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>833655</t>
+          <t>834836</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>848020</t>
+          <t>846851</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>896640</t>
+          <t>895586</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1659328</t>
+          <t>1655659</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1720166</t>
+          <t>1720810</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,91%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>417913</t>
+          <t>416507</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>490096</t>
+          <t>494851</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>494083</t>
+          <t>490061</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>574991</t>
+          <t>578056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>933527</t>
+          <t>932541</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1045896</t>
+          <t>1048028</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2784683</t>
+          <t>2779928</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2856866</t>
+          <t>2858272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,24%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2802309</t>
+          <t>2799244</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2883217</t>
+          <t>2887239</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5606183</t>
+          <t>5604051</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5718552</t>
+          <t>5719538</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>85,97%</t>
+          <t>85,98%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121851</t>
+          <t>121866</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>165520</t>
+          <t>164265</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>111995</t>
+          <t>113885</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>155036</t>
+          <t>154912</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>245220</t>
+          <t>242250</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303989</t>
+          <t>305791</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>536922</t>
+          <t>538177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>580591</t>
+          <t>580576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,44%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>542014</t>
+          <t>542138</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>585055</t>
+          <t>583165</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1095503</t>
+          <t>1093701</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1154272</t>
+          <t>1157242</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>78,28%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>154712</t>
+          <t>156318</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>204455</t>
+          <t>207960</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>165846</t>
+          <t>165961</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>221269</t>
+          <t>216303</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>336098</t>
+          <t>337373</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408625</t>
+          <t>406113</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,4%</t>
+          <t>16,46%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,82%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>813492</t>
+          <t>809987</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>863235</t>
+          <t>861629</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>809844</t>
+          <t>814810</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>865267</t>
+          <t>865152</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1640435</t>
+          <t>1642947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1712962</t>
+          <t>1711687</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,6%</t>
+          <t>83,54%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>98600</t>
+          <t>98789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142957</t>
+          <t>143040</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112573</t>
+          <t>111882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>157259</t>
+          <t>156827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221989</t>
+          <t>222314</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>285226</t>
+          <t>287593</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>18,75%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613661</t>
+          <t>613578</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>658018</t>
+          <t>657829</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>619915</t>
+          <t>620347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>664601</t>
+          <t>665292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>79,77%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1248566</t>
+          <t>1246199</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1311803</t>
+          <t>1311478</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>81,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>85,51%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140276</t>
+          <t>141584</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>189903</t>
+          <t>191207</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>167770</t>
+          <t>166985</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>217708</t>
+          <t>219853</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>321255</t>
+          <t>322167</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>392387</t>
+          <t>389688</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,52%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>754845</t>
+          <t>753541</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>804472</t>
+          <t>803164</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>79,9%</t>
+          <t>79,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>834193</t>
+          <t>832048</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>884131</t>
+          <t>884916</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1604262</t>
+          <t>1606961</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1675394</t>
+          <t>1674482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>561934</t>
+          <t>559303</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>651223</t>
+          <t>651651</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>603682</t>
+          <t>601675</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>697331</t>
+          <t>696575</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1180465</t>
+          <t>1188590</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1318056</t>
+          <t>1322663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,95%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2770532</t>
+          <t>2770104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2859821</t>
+          <t>2862452</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2859907</t>
+          <t>2860663</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2953556</t>
+          <t>2955563</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5660937</t>
+          <t>5656330</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5798528</t>
+          <t>5790403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,11%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>82,97%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>97776</t>
+          <t>96398</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>135793</t>
+          <t>136406</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99607</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>139958</t>
+          <t>141110</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>208760</t>
+          <t>209941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>262241</t>
+          <t>263150</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,53%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>539007</t>
+          <t>538394</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>577024</t>
+          <t>578402</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,88%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>532881</t>
+          <t>531729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>573232</t>
+          <t>572490</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1085398</t>
+          <t>1084489</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1138879</t>
+          <t>1137698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,54%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,42%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>126992</t>
+          <t>126361</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>168942</t>
+          <t>170552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>160217</t>
+          <t>162270</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>214477</t>
+          <t>215579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>301833</t>
+          <t>302398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>372419</t>
+          <t>370517</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>853489</t>
+          <t>851879</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>895439</t>
+          <t>896070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>828436</t>
+          <t>827334</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>882696</t>
+          <t>880643</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,43%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1692925</t>
+          <t>1694827</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1763511</t>
+          <t>1762946</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,97%</t>
+          <t>82,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,36%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106400</t>
+          <t>104946</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>149612</t>
+          <t>147770</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>102235</t>
+          <t>101378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>148027</t>
+          <t>145522</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>221502</t>
+          <t>221119</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>282110</t>
+          <t>277817</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>609940</t>
+          <t>611782</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>653152</t>
+          <t>654606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,3%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>636984</t>
+          <t>639489</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>682776</t>
+          <t>683633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1262453</t>
+          <t>1266746</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1323061</t>
+          <t>1323444</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,68%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>122313</t>
+          <t>121700</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>165634</t>
+          <t>165763</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>156075</t>
+          <t>157781</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>210376</t>
+          <t>209421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>296146</t>
+          <t>293185</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>364532</t>
+          <t>363734</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,4%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>771933</t>
+          <t>771804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>815254</t>
+          <t>815867</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,33%</t>
+          <t>82,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>833403</t>
+          <t>834358</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>887704</t>
+          <t>885998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>79,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1616814</t>
+          <t>1617612</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1685200</t>
+          <t>1688161</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,6%</t>
+          <t>81,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>85,2%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>496907</t>
+          <t>492829</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>576882</t>
+          <t>574832</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>568059</t>
+          <t>564882</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>664023</t>
+          <t>667564</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1085633</t>
+          <t>1088262</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1210414</t>
+          <t>1210238</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2817468</t>
+          <t>2819518</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2897443</t>
+          <t>2901521</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,36%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2880519</t>
+          <t>2876978</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2976483</t>
+          <t>2979660</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,27%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5728478</t>
+          <t>5728654</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5853259</t>
+          <t>5850630</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,32%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>201201</t>
+          <t>222038</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>177703</t>
+          <t>199863</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>224456</t>
+          <t>248533</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>32,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>255361</t>
+          <t>274383</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>236220</t>
+          <t>253916</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>273629</t>
+          <t>295137</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>456562</t>
+          <t>496420</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>423896</t>
+          <t>463374</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>487781</t>
+          <t>527391</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,21%</t>
+          <t>37,05%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>434240</t>
+          <t>468672</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410985</t>
+          <t>442177</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>457738</t>
+          <t>490847</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>67,85%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,68%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>420009</t>
+          <t>458339</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>401741</t>
+          <t>437585</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>439150</t>
+          <t>478806</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>854249</t>
+          <t>927011</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>823030</t>
+          <t>896040</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>886915</t>
+          <t>960057</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,45%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>257161</t>
+          <t>280440</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>121932</t>
+          <t>252534</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>336549</t>
+          <t>312554</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>24,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>343350</t>
+          <t>381963</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>319719</t>
+          <t>355209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>367975</t>
+          <t>410013</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,37%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>600511</t>
+          <t>662403</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>398484</t>
+          <t>622789</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>690172</t>
+          <t>702339</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>935703</t>
+          <t>768477</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>856315</t>
+          <t>736363</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1070932</t>
+          <t>796383</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>614756</t>
+          <t>688875</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>590131</t>
+          <t>660825</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>638387</t>
+          <t>715629</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,59%</t>
+          <t>61,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1550460</t>
+          <t>1457352</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1460799</t>
+          <t>1417416</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1752487</t>
+          <t>1496966</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>66,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>70,62%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>210330</t>
+          <t>238834</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>184096</t>
+          <t>210069</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>235680</t>
+          <t>265814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,12%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>433928</t>
+          <t>259894</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>281024</t>
+          <t>237535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>684962</t>
+          <t>283368</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,49%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>644258</t>
+          <t>498727</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>484135</t>
+          <t>464218</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>959421</t>
+          <t>535872</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>30,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>33,17%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>494350</t>
+          <t>564239</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>469000</t>
+          <t>537259</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>520584</t>
+          <t>593004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,88%</t>
+          <t>73,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>499438</t>
+          <t>552365</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>248404</t>
+          <t>528891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>652342</t>
+          <t>574724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,51%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,61%</t>
+          <t>65,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>993788</t>
+          <t>1116605</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>678625</t>
+          <t>1079460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1153911</t>
+          <t>1151114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>60,67%</t>
+          <t>69,13%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>71,26%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>334750</t>
+          <t>351124</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>306608</t>
+          <t>319542</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>367671</t>
+          <t>381143</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>35,46%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>38,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>395937</t>
+          <t>427813</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>324400</t>
+          <t>401001</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>436301</t>
+          <t>454033</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>730687</t>
+          <t>778937</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>642055</t>
+          <t>739907</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>776731</t>
+          <t>819523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,18%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,87%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>592081</t>
+          <t>638938</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>559160</t>
+          <t>608919</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>620223</t>
+          <t>670520</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>61,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>696656</t>
+          <t>690506</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>656292</t>
+          <t>664286</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>768193</t>
+          <t>717318</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1288737</t>
+          <t>1329444</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1242693</t>
+          <t>1288858</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1377369</t>
+          <t>1368474</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>63,82%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>64,91%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1003443</t>
+          <t>1092435</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>761251</t>
+          <t>1038257</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1094074</t>
+          <t>1148687</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>29,0%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1428576</t>
+          <t>1344053</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1272239</t>
+          <t>1296631</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1826627</t>
+          <t>1403302</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>35,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,77%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>49,92%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>2432019</t>
+          <t>2436488</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2207379</t>
+          <t>2365011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2865676</t>
+          <t>2513361</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>34,59%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2456374</t>
+          <t>2440327</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2365743</t>
+          <t>2384075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2698566</t>
+          <t>2494505</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>71,0%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2230859</t>
+          <t>2390084</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1832808</t>
+          <t>2330835</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2387196</t>
+          <t>2437506</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>64,01%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>65,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>4687233</t>
+          <t>4830411</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>4253576</t>
+          <t>4753538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4911873</t>
+          <t>4901888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>67,46%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3659435</t>
+          <t>3734137</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7119252</t>
+          <t>7266899</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
